--- a/PADRAO_APURACAO.xlsx
+++ b/PADRAO_APURACAO.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\TAINA\B3\CALCULADORA\ApurarB3\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2CD170C-91C3-4668-AD23-DB8E9CB69CD8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4985221D-44DB-452F-B33E-DA9758230C76}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E4F4D1A-8745-46D1-9297-3206C2CF753A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{0E4F4D1A-8745-46D1-9297-3206C2CF753A}"/>
   </bookViews>
   <sheets>
     <sheet name="2026" sheetId="17" r:id="rId1"/>
@@ -1207,66 +1207,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left"/>
+    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="166" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="16" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1283,7 +1247,43 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="19" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="17" fontId="25" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="25" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="25" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="17" fontId="25" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1295,61 +1295,61 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="14" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="3" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="14" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="17" fontId="25" fillId="8" borderId="20" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="25" fillId="8" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="17" fontId="25" fillId="8" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="13" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="166" fontId="8" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="13" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="16" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="5" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="17" fontId="25" fillId="8" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="11" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="14" fontId="8" fillId="2" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="5" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="18" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="19" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Moeda" xfId="1" builtinId="4"/>
@@ -1362,21 +1362,21 @@
   <dxfs count="3">
     <dxf>
       <font>
+        <color rgb="FF9C0006"/>
+      </font>
+      <fill>
+        <patternFill>
+          <bgColor rgb="FFFFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
         <color rgb="FF006100"/>
       </font>
       <fill>
         <patternFill>
           <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
         </patternFill>
       </fill>
     </dxf>
@@ -5361,8 +5361,8 @@
       <c r="H3" s="89"/>
       <c r="I3" s="89"/>
       <c r="J3" s="89"/>
-      <c r="K3" s="135"/>
-      <c r="L3" s="129"/>
+      <c r="K3" s="105"/>
+      <c r="L3" s="106"/>
       <c r="M3" s="53"/>
       <c r="N3" s="43"/>
       <c r="O3" s="88"/>
@@ -5385,8 +5385,8 @@
       <c r="H4" s="89"/>
       <c r="I4" s="89"/>
       <c r="J4" s="89"/>
-      <c r="K4" s="135"/>
-      <c r="L4" s="129"/>
+      <c r="K4" s="105"/>
+      <c r="L4" s="106"/>
       <c r="M4" s="53"/>
       <c r="N4" s="54" t="str">
         <f>G4</f>
@@ -5468,33 +5468,33 @@
       <c r="U7" s="49"/>
     </row>
     <row r="8" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="145" t="s">
+      <c r="A8" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="B8" s="146"/>
-      <c r="C8" s="146"/>
-      <c r="D8" s="146"/>
-      <c r="E8" s="146"/>
-      <c r="F8" s="147"/>
-      <c r="G8" s="148" t="s">
+      <c r="B8" s="125"/>
+      <c r="C8" s="125"/>
+      <c r="D8" s="125"/>
+      <c r="E8" s="125"/>
+      <c r="F8" s="126"/>
+      <c r="G8" s="120" t="s">
         <v>104</v>
       </c>
-      <c r="H8" s="149"/>
-      <c r="I8" s="149"/>
-      <c r="J8" s="149"/>
-      <c r="K8" s="149"/>
-      <c r="L8" s="149"/>
-      <c r="M8" s="150"/>
-      <c r="N8" s="148" t="s">
+      <c r="H8" s="121"/>
+      <c r="I8" s="121"/>
+      <c r="J8" s="121"/>
+      <c r="K8" s="121"/>
+      <c r="L8" s="121"/>
+      <c r="M8" s="122"/>
+      <c r="N8" s="120" t="s">
         <v>104</v>
       </c>
-      <c r="O8" s="149"/>
-      <c r="P8" s="149"/>
-      <c r="Q8" s="149"/>
-      <c r="R8" s="149"/>
-      <c r="S8" s="149"/>
-      <c r="T8" s="149"/>
-      <c r="U8" s="150"/>
+      <c r="O8" s="121"/>
+      <c r="P8" s="121"/>
+      <c r="Q8" s="121"/>
+      <c r="R8" s="121"/>
+      <c r="S8" s="121"/>
+      <c r="T8" s="121"/>
+      <c r="U8" s="122"/>
     </row>
     <row r="9" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="57"/>
@@ -5506,29 +5506,29 @@
     </row>
     <row r="10" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="57"/>
-      <c r="B10" s="139" t="s">
+      <c r="B10" s="107" t="s">
         <v>100</v>
       </c>
-      <c r="C10" s="140"/>
-      <c r="D10" s="140"/>
-      <c r="E10" s="141"/>
+      <c r="C10" s="108"/>
+      <c r="D10" s="108"/>
+      <c r="E10" s="109"/>
       <c r="F10" s="49"/>
       <c r="G10" s="57"/>
-      <c r="H10" s="139" t="s">
+      <c r="H10" s="107" t="s">
         <v>99</v>
       </c>
-      <c r="I10" s="140"/>
-      <c r="J10" s="140"/>
-      <c r="K10" s="140"/>
-      <c r="L10" s="141"/>
+      <c r="I10" s="108"/>
+      <c r="J10" s="108"/>
+      <c r="K10" s="108"/>
+      <c r="L10" s="109"/>
       <c r="M10" s="49"/>
       <c r="N10" s="57"/>
-      <c r="P10" s="139" t="s">
+      <c r="P10" s="107" t="s">
         <v>98</v>
       </c>
-      <c r="Q10" s="140"/>
-      <c r="R10" s="140"/>
-      <c r="S10" s="141"/>
+      <c r="Q10" s="108"/>
+      <c r="R10" s="108"/>
+      <c r="S10" s="109"/>
       <c r="U10" s="49"/>
     </row>
     <row r="11" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -5580,11 +5580,11 @@
     </row>
     <row r="12" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A12" s="57"/>
-      <c r="B12" s="153" t="s">
+      <c r="B12" s="129" t="s">
         <v>78</v>
       </c>
-      <c r="C12" s="140"/>
-      <c r="D12" s="141"/>
+      <c r="C12" s="108"/>
+      <c r="D12" s="109"/>
       <c r="E12" s="62">
         <v>0</v>
       </c>
@@ -6020,12 +6020,12 @@
     </row>
     <row r="30" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="57"/>
-      <c r="B30" s="139" t="s">
+      <c r="B30" s="107" t="s">
         <v>90</v>
       </c>
-      <c r="C30" s="139"/>
-      <c r="D30" s="139"/>
-      <c r="E30" s="139"/>
+      <c r="C30" s="107"/>
+      <c r="D30" s="107"/>
+      <c r="E30" s="107"/>
       <c r="F30" s="49"/>
       <c r="G30" s="71"/>
       <c r="H30" s="63"/>
@@ -6034,16 +6034,16 @@
       <c r="K30" s="65"/>
       <c r="L30" s="66"/>
       <c r="M30" s="51"/>
-      <c r="N30" s="148" t="s">
+      <c r="N30" s="120" t="s">
         <v>104</v>
       </c>
-      <c r="O30" s="149"/>
-      <c r="P30" s="149"/>
-      <c r="Q30" s="149"/>
-      <c r="R30" s="149"/>
-      <c r="S30" s="149"/>
-      <c r="T30" s="149"/>
-      <c r="U30" s="150"/>
+      <c r="O30" s="121"/>
+      <c r="P30" s="121"/>
+      <c r="Q30" s="121"/>
+      <c r="R30" s="121"/>
+      <c r="S30" s="121"/>
+      <c r="T30" s="121"/>
+      <c r="U30" s="122"/>
     </row>
     <row r="31" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A31" s="57"/>
@@ -6073,11 +6073,11 @@
     </row>
     <row r="32" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A32" s="57"/>
-      <c r="B32" s="142" t="s">
+      <c r="B32" s="117" t="s">
         <v>78</v>
       </c>
-      <c r="C32" s="143"/>
-      <c r="D32" s="144"/>
+      <c r="C32" s="118"/>
+      <c r="D32" s="119"/>
       <c r="E32" s="62">
         <v>0</v>
       </c>
@@ -6118,14 +6118,14 @@
       <c r="L33" s="66"/>
       <c r="M33" s="51"/>
       <c r="N33" s="50"/>
-      <c r="O33" s="139" t="s">
+      <c r="O33" s="107" t="s">
         <v>107</v>
       </c>
-      <c r="P33" s="140"/>
-      <c r="Q33" s="140"/>
-      <c r="R33" s="140"/>
-      <c r="S33" s="140"/>
-      <c r="T33" s="141"/>
+      <c r="P33" s="108"/>
+      <c r="Q33" s="108"/>
+      <c r="R33" s="108"/>
+      <c r="S33" s="108"/>
+      <c r="T33" s="109"/>
       <c r="U33" s="49"/>
     </row>
     <row r="34" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -6154,10 +6154,10 @@
       <c r="L34" s="66"/>
       <c r="M34" s="51"/>
       <c r="N34" s="50"/>
-      <c r="O34" s="152" t="s">
+      <c r="O34" s="128" t="s">
         <v>89</v>
       </c>
-      <c r="P34" s="141"/>
+      <c r="P34" s="109"/>
       <c r="Q34" s="60" t="s">
         <v>88</v>
       </c>
@@ -6198,8 +6198,8 @@
       <c r="L35" s="66"/>
       <c r="M35" s="51"/>
       <c r="N35" s="50"/>
-      <c r="O35" s="154"/>
-      <c r="P35" s="141"/>
+      <c r="O35" s="110"/>
+      <c r="P35" s="109"/>
       <c r="Q35" s="67"/>
       <c r="R35" s="67"/>
       <c r="S35" s="67"/>
@@ -6232,8 +6232,8 @@
       <c r="L36" s="66"/>
       <c r="M36" s="51"/>
       <c r="N36" s="50"/>
-      <c r="O36" s="154"/>
-      <c r="P36" s="141"/>
+      <c r="O36" s="110"/>
+      <c r="P36" s="109"/>
       <c r="Q36" s="67"/>
       <c r="R36" s="67"/>
       <c r="S36" s="67"/>
@@ -6266,8 +6266,8 @@
       <c r="L37" s="66"/>
       <c r="M37" s="51"/>
       <c r="N37" s="50"/>
-      <c r="O37" s="154"/>
-      <c r="P37" s="141"/>
+      <c r="O37" s="110"/>
+      <c r="P37" s="109"/>
       <c r="Q37" s="67"/>
       <c r="R37" s="67"/>
       <c r="S37" s="67"/>
@@ -6300,8 +6300,8 @@
       <c r="L38" s="66"/>
       <c r="M38" s="51"/>
       <c r="N38" s="50"/>
-      <c r="O38" s="154"/>
-      <c r="P38" s="141"/>
+      <c r="O38" s="110"/>
+      <c r="P38" s="109"/>
       <c r="Q38" s="67"/>
       <c r="R38" s="67"/>
       <c r="S38" s="67"/>
@@ -6467,11 +6467,11 @@
       </c>
       <c r="F44" s="49"/>
       <c r="G44" s="57"/>
-      <c r="H44" s="151" t="s">
+      <c r="H44" s="127" t="s">
         <v>85</v>
       </c>
-      <c r="I44" s="140"/>
-      <c r="J44" s="141"/>
+      <c r="I44" s="108"/>
+      <c r="J44" s="109"/>
       <c r="K44" s="72">
         <f>SUM(K12:K38)</f>
         <v>0</v>
@@ -6498,73 +6498,73 @@
       <c r="U46" s="49"/>
     </row>
     <row r="47" spans="1:21" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="128"/>
-      <c r="B47" s="129"/>
-      <c r="C47" s="129"/>
-      <c r="D47" s="129"/>
-      <c r="E47" s="129"/>
-      <c r="F47" s="130"/>
-      <c r="G47" s="128"/>
-      <c r="H47" s="129"/>
-      <c r="I47" s="129"/>
-      <c r="J47" s="129"/>
-      <c r="K47" s="129"/>
-      <c r="L47" s="129"/>
-      <c r="M47" s="130"/>
-      <c r="N47" s="128"/>
-      <c r="O47" s="129"/>
-      <c r="P47" s="129"/>
-      <c r="Q47" s="129"/>
-      <c r="R47" s="129"/>
-      <c r="S47" s="129"/>
-      <c r="T47" s="129"/>
-      <c r="U47" s="130"/>
+      <c r="A47" s="111"/>
+      <c r="B47" s="106"/>
+      <c r="C47" s="106"/>
+      <c r="D47" s="106"/>
+      <c r="E47" s="106"/>
+      <c r="F47" s="112"/>
+      <c r="G47" s="111"/>
+      <c r="H47" s="106"/>
+      <c r="I47" s="106"/>
+      <c r="J47" s="106"/>
+      <c r="K47" s="106"/>
+      <c r="L47" s="106"/>
+      <c r="M47" s="112"/>
+      <c r="N47" s="111"/>
+      <c r="O47" s="106"/>
+      <c r="P47" s="106"/>
+      <c r="Q47" s="106"/>
+      <c r="R47" s="106"/>
+      <c r="S47" s="106"/>
+      <c r="T47" s="106"/>
+      <c r="U47" s="112"/>
     </row>
     <row r="48" spans="1:21" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="131"/>
-      <c r="B48" s="129"/>
-      <c r="C48" s="129"/>
-      <c r="D48" s="129"/>
-      <c r="E48" s="129"/>
-      <c r="F48" s="130"/>
-      <c r="G48" s="131"/>
-      <c r="H48" s="129"/>
-      <c r="I48" s="129"/>
-      <c r="J48" s="129"/>
-      <c r="K48" s="129"/>
-      <c r="L48" s="129"/>
-      <c r="M48" s="130"/>
-      <c r="N48" s="131"/>
-      <c r="O48" s="129"/>
-      <c r="P48" s="129"/>
-      <c r="Q48" s="129"/>
-      <c r="R48" s="129"/>
-      <c r="S48" s="129"/>
-      <c r="T48" s="129"/>
-      <c r="U48" s="130"/>
+      <c r="A48" s="113"/>
+      <c r="B48" s="106"/>
+      <c r="C48" s="106"/>
+      <c r="D48" s="106"/>
+      <c r="E48" s="106"/>
+      <c r="F48" s="112"/>
+      <c r="G48" s="113"/>
+      <c r="H48" s="106"/>
+      <c r="I48" s="106"/>
+      <c r="J48" s="106"/>
+      <c r="K48" s="106"/>
+      <c r="L48" s="106"/>
+      <c r="M48" s="112"/>
+      <c r="N48" s="113"/>
+      <c r="O48" s="106"/>
+      <c r="P48" s="106"/>
+      <c r="Q48" s="106"/>
+      <c r="R48" s="106"/>
+      <c r="S48" s="106"/>
+      <c r="T48" s="106"/>
+      <c r="U48" s="112"/>
     </row>
     <row r="49" spans="1:21" ht="20.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="132"/>
-      <c r="B49" s="133"/>
-      <c r="C49" s="133"/>
-      <c r="D49" s="133"/>
-      <c r="E49" s="133"/>
-      <c r="F49" s="134"/>
-      <c r="G49" s="132"/>
-      <c r="H49" s="133"/>
-      <c r="I49" s="133"/>
-      <c r="J49" s="133"/>
-      <c r="K49" s="133"/>
-      <c r="L49" s="133"/>
-      <c r="M49" s="134"/>
-      <c r="N49" s="132"/>
-      <c r="O49" s="133"/>
-      <c r="P49" s="133"/>
-      <c r="Q49" s="133"/>
-      <c r="R49" s="133"/>
-      <c r="S49" s="133"/>
-      <c r="T49" s="133"/>
-      <c r="U49" s="134"/>
+      <c r="A49" s="114"/>
+      <c r="B49" s="115"/>
+      <c r="C49" s="115"/>
+      <c r="D49" s="115"/>
+      <c r="E49" s="115"/>
+      <c r="F49" s="116"/>
+      <c r="G49" s="114"/>
+      <c r="H49" s="115"/>
+      <c r="I49" s="115"/>
+      <c r="J49" s="115"/>
+      <c r="K49" s="115"/>
+      <c r="L49" s="115"/>
+      <c r="M49" s="116"/>
+      <c r="N49" s="114"/>
+      <c r="O49" s="115"/>
+      <c r="P49" s="115"/>
+      <c r="Q49" s="115"/>
+      <c r="R49" s="115"/>
+      <c r="S49" s="115"/>
+      <c r="T49" s="115"/>
+      <c r="U49" s="116"/>
     </row>
     <row r="50" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A50" s="45"/>
@@ -6621,8 +6621,8 @@
       <c r="H52" s="89"/>
       <c r="I52" s="89"/>
       <c r="J52" s="89"/>
-      <c r="K52" s="135"/>
-      <c r="L52" s="129"/>
+      <c r="K52" s="105"/>
+      <c r="L52" s="106"/>
       <c r="M52" s="53"/>
       <c r="N52" s="43"/>
       <c r="O52" s="88"/>
@@ -6646,8 +6646,8 @@
       <c r="H53" s="89"/>
       <c r="I53" s="89"/>
       <c r="J53" s="89"/>
-      <c r="K53" s="135"/>
-      <c r="L53" s="129"/>
+      <c r="K53" s="105"/>
+      <c r="L53" s="106"/>
       <c r="M53" s="53"/>
       <c r="N53" s="54" t="str">
         <f>G53</f>
@@ -6731,33 +6731,33 @@
       <c r="U56" s="49"/>
     </row>
     <row r="57" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A57" s="145" t="s">
+      <c r="A57" s="124" t="s">
         <v>101</v>
       </c>
-      <c r="B57" s="146"/>
-      <c r="C57" s="146"/>
-      <c r="D57" s="146"/>
-      <c r="E57" s="146"/>
-      <c r="F57" s="147"/>
-      <c r="G57" s="148" t="s">
+      <c r="B57" s="125"/>
+      <c r="C57" s="125"/>
+      <c r="D57" s="125"/>
+      <c r="E57" s="125"/>
+      <c r="F57" s="126"/>
+      <c r="G57" s="120" t="s">
         <v>84</v>
       </c>
-      <c r="H57" s="149"/>
-      <c r="I57" s="149"/>
-      <c r="J57" s="149"/>
-      <c r="K57" s="149"/>
-      <c r="L57" s="149"/>
-      <c r="M57" s="150"/>
-      <c r="N57" s="148" t="s">
+      <c r="H57" s="121"/>
+      <c r="I57" s="121"/>
+      <c r="J57" s="121"/>
+      <c r="K57" s="121"/>
+      <c r="L57" s="121"/>
+      <c r="M57" s="122"/>
+      <c r="N57" s="120" t="s">
         <v>83</v>
       </c>
-      <c r="O57" s="149"/>
-      <c r="P57" s="149"/>
-      <c r="Q57" s="149"/>
-      <c r="R57" s="149"/>
-      <c r="S57" s="149"/>
-      <c r="T57" s="149"/>
-      <c r="U57" s="150"/>
+      <c r="O57" s="121"/>
+      <c r="P57" s="121"/>
+      <c r="Q57" s="121"/>
+      <c r="R57" s="121"/>
+      <c r="S57" s="121"/>
+      <c r="T57" s="121"/>
+      <c r="U57" s="122"/>
     </row>
     <row r="58" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A58" s="57"/>
@@ -6769,12 +6769,12 @@
     </row>
     <row r="59" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A59" s="57"/>
-      <c r="B59" s="136" t="s">
+      <c r="B59" s="130" t="s">
         <v>82</v>
       </c>
-      <c r="C59" s="137"/>
-      <c r="D59" s="137"/>
-      <c r="E59" s="138"/>
+      <c r="C59" s="131"/>
+      <c r="D59" s="131"/>
+      <c r="E59" s="132"/>
       <c r="F59" s="49"/>
       <c r="G59" s="57"/>
       <c r="M59" s="49"/>
@@ -6803,11 +6803,11 @@
     </row>
     <row r="61" spans="1:21" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A61" s="57"/>
-      <c r="B61" s="142" t="s">
+      <c r="B61" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="C61" s="143"/>
-      <c r="D61" s="144"/>
+      <c r="C61" s="118"/>
+      <c r="D61" s="119"/>
       <c r="E61" s="62">
         <v>0</v>
       </c>
@@ -7280,73 +7280,73 @@
       <c r="U95" s="49"/>
     </row>
     <row r="96" spans="1:21" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A96" s="128"/>
-      <c r="B96" s="129"/>
-      <c r="C96" s="129"/>
-      <c r="D96" s="129"/>
-      <c r="E96" s="129"/>
-      <c r="F96" s="130"/>
-      <c r="G96" s="128"/>
-      <c r="H96" s="129"/>
-      <c r="I96" s="129"/>
-      <c r="J96" s="129"/>
-      <c r="K96" s="129"/>
-      <c r="L96" s="129"/>
-      <c r="M96" s="130"/>
-      <c r="N96" s="128"/>
-      <c r="O96" s="129"/>
-      <c r="P96" s="129"/>
-      <c r="Q96" s="129"/>
-      <c r="R96" s="129"/>
-      <c r="S96" s="129"/>
-      <c r="T96" s="129"/>
-      <c r="U96" s="130"/>
+      <c r="A96" s="111"/>
+      <c r="B96" s="106"/>
+      <c r="C96" s="106"/>
+      <c r="D96" s="106"/>
+      <c r="E96" s="106"/>
+      <c r="F96" s="112"/>
+      <c r="G96" s="111"/>
+      <c r="H96" s="106"/>
+      <c r="I96" s="106"/>
+      <c r="J96" s="106"/>
+      <c r="K96" s="106"/>
+      <c r="L96" s="106"/>
+      <c r="M96" s="112"/>
+      <c r="N96" s="111"/>
+      <c r="O96" s="106"/>
+      <c r="P96" s="106"/>
+      <c r="Q96" s="106"/>
+      <c r="R96" s="106"/>
+      <c r="S96" s="106"/>
+      <c r="T96" s="106"/>
+      <c r="U96" s="112"/>
     </row>
     <row r="97" spans="1:21" x14ac:dyDescent="0.25">
-      <c r="A97" s="131"/>
-      <c r="B97" s="129"/>
-      <c r="C97" s="129"/>
-      <c r="D97" s="129"/>
-      <c r="E97" s="129"/>
-      <c r="F97" s="130"/>
-      <c r="G97" s="131"/>
-      <c r="H97" s="129"/>
-      <c r="I97" s="129"/>
-      <c r="J97" s="129"/>
-      <c r="K97" s="129"/>
-      <c r="L97" s="129"/>
-      <c r="M97" s="130"/>
-      <c r="N97" s="131"/>
-      <c r="O97" s="129"/>
-      <c r="P97" s="129"/>
-      <c r="Q97" s="129"/>
-      <c r="R97" s="129"/>
-      <c r="S97" s="129"/>
-      <c r="T97" s="129"/>
-      <c r="U97" s="130"/>
+      <c r="A97" s="113"/>
+      <c r="B97" s="106"/>
+      <c r="C97" s="106"/>
+      <c r="D97" s="106"/>
+      <c r="E97" s="106"/>
+      <c r="F97" s="112"/>
+      <c r="G97" s="113"/>
+      <c r="H97" s="106"/>
+      <c r="I97" s="106"/>
+      <c r="J97" s="106"/>
+      <c r="K97" s="106"/>
+      <c r="L97" s="106"/>
+      <c r="M97" s="112"/>
+      <c r="N97" s="113"/>
+      <c r="O97" s="106"/>
+      <c r="P97" s="106"/>
+      <c r="Q97" s="106"/>
+      <c r="R97" s="106"/>
+      <c r="S97" s="106"/>
+      <c r="T97" s="106"/>
+      <c r="U97" s="112"/>
     </row>
     <row r="98" spans="1:21" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A98" s="132"/>
-      <c r="B98" s="133"/>
-      <c r="C98" s="133"/>
-      <c r="D98" s="133"/>
-      <c r="E98" s="133"/>
-      <c r="F98" s="134"/>
-      <c r="G98" s="132"/>
-      <c r="H98" s="133"/>
-      <c r="I98" s="133"/>
-      <c r="J98" s="133"/>
-      <c r="K98" s="133"/>
-      <c r="L98" s="133"/>
-      <c r="M98" s="134"/>
-      <c r="N98" s="132"/>
-      <c r="O98" s="133"/>
-      <c r="P98" s="133"/>
-      <c r="Q98" s="133"/>
-      <c r="R98" s="133"/>
-      <c r="S98" s="133"/>
-      <c r="T98" s="133"/>
-      <c r="U98" s="134"/>
+      <c r="A98" s="114"/>
+      <c r="B98" s="115"/>
+      <c r="C98" s="115"/>
+      <c r="D98" s="115"/>
+      <c r="E98" s="115"/>
+      <c r="F98" s="116"/>
+      <c r="G98" s="114"/>
+      <c r="H98" s="115"/>
+      <c r="I98" s="115"/>
+      <c r="J98" s="115"/>
+      <c r="K98" s="115"/>
+      <c r="L98" s="115"/>
+      <c r="M98" s="116"/>
+      <c r="N98" s="114"/>
+      <c r="O98" s="115"/>
+      <c r="P98" s="115"/>
+      <c r="Q98" s="115"/>
+      <c r="R98" s="115"/>
+      <c r="S98" s="115"/>
+      <c r="T98" s="115"/>
+      <c r="U98" s="116"/>
     </row>
     <row r="99" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A99" s="45"/>
@@ -7406,14 +7406,14 @@
       <c r="F105" s="49"/>
     </row>
     <row r="106" spans="1:21" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A106" s="155" t="s">
+      <c r="A106" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="B106" s="149"/>
-      <c r="C106" s="149"/>
-      <c r="D106" s="149"/>
-      <c r="E106" s="149"/>
-      <c r="F106" s="150"/>
+      <c r="B106" s="121"/>
+      <c r="C106" s="121"/>
+      <c r="D106" s="121"/>
+      <c r="E106" s="121"/>
+      <c r="F106" s="122"/>
     </row>
     <row r="107" spans="1:21" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A107" s="57"/>
@@ -7421,12 +7421,12 @@
     </row>
     <row r="108" spans="1:21" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A108" s="75"/>
-      <c r="B108" s="139" t="s">
+      <c r="B108" s="107" t="s">
         <v>77</v>
       </c>
-      <c r="C108" s="140"/>
-      <c r="D108" s="140"/>
-      <c r="E108" s="141"/>
+      <c r="C108" s="108"/>
+      <c r="D108" s="108"/>
+      <c r="E108" s="109"/>
       <c r="F108" s="76"/>
     </row>
     <row r="109" spans="1:21" x14ac:dyDescent="0.25">
@@ -7687,12 +7687,12 @@
     </row>
     <row r="124" spans="1:6" ht="15.6" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A124" s="57"/>
-      <c r="B124" s="139" t="s">
+      <c r="B124" s="107" t="s">
         <v>76</v>
       </c>
-      <c r="C124" s="140"/>
-      <c r="D124" s="140"/>
-      <c r="E124" s="141"/>
+      <c r="C124" s="108"/>
+      <c r="D124" s="108"/>
+      <c r="E124" s="109"/>
       <c r="F124" s="49"/>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.25">
@@ -7972,28 +7972,28 @@
       <c r="F144" s="49"/>
     </row>
     <row r="145" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A145" s="128"/>
-      <c r="B145" s="129"/>
-      <c r="C145" s="129"/>
-      <c r="D145" s="129"/>
-      <c r="E145" s="129"/>
-      <c r="F145" s="130"/>
+      <c r="A145" s="111"/>
+      <c r="B145" s="106"/>
+      <c r="C145" s="106"/>
+      <c r="D145" s="106"/>
+      <c r="E145" s="106"/>
+      <c r="F145" s="112"/>
     </row>
     <row r="146" spans="1:6" ht="12" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A146" s="131"/>
-      <c r="B146" s="129"/>
-      <c r="C146" s="129"/>
-      <c r="D146" s="129"/>
-      <c r="E146" s="129"/>
-      <c r="F146" s="130"/>
+      <c r="A146" s="113"/>
+      <c r="B146" s="106"/>
+      <c r="C146" s="106"/>
+      <c r="D146" s="106"/>
+      <c r="E146" s="106"/>
+      <c r="F146" s="112"/>
     </row>
     <row r="147" spans="1:6" ht="13.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A147" s="132"/>
-      <c r="B147" s="133"/>
-      <c r="C147" s="133"/>
-      <c r="D147" s="133"/>
-      <c r="E147" s="133"/>
-      <c r="F147" s="134"/>
+      <c r="A147" s="114"/>
+      <c r="B147" s="115"/>
+      <c r="C147" s="115"/>
+      <c r="D147" s="115"/>
+      <c r="E147" s="115"/>
+      <c r="F147" s="116"/>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A148" s="45"/>
@@ -8053,14 +8053,14 @@
       <c r="F154" s="49"/>
     </row>
     <row r="155" spans="1:6" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A155" s="155" t="s">
+      <c r="A155" s="123" t="s">
         <v>106</v>
       </c>
-      <c r="B155" s="149"/>
-      <c r="C155" s="149"/>
-      <c r="D155" s="149"/>
-      <c r="E155" s="149"/>
-      <c r="F155" s="150"/>
+      <c r="B155" s="121"/>
+      <c r="C155" s="121"/>
+      <c r="D155" s="121"/>
+      <c r="E155" s="121"/>
+      <c r="F155" s="122"/>
     </row>
     <row r="156" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A156" s="57"/>
@@ -8068,12 +8068,12 @@
     </row>
     <row r="157" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A157" s="75"/>
-      <c r="B157" s="139" t="s">
+      <c r="B157" s="107" t="s">
         <v>72</v>
       </c>
-      <c r="C157" s="140"/>
-      <c r="D157" s="140"/>
-      <c r="E157" s="141"/>
+      <c r="C157" s="108"/>
+      <c r="D157" s="108"/>
+      <c r="E157" s="109"/>
       <c r="F157" s="76"/>
     </row>
     <row r="158" spans="1:6" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -8409,34 +8409,57 @@
       <c r="F194" s="49"/>
     </row>
     <row r="195" spans="1:6" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A195" s="128"/>
-      <c r="B195" s="129"/>
-      <c r="C195" s="129"/>
-      <c r="D195" s="129"/>
-      <c r="E195" s="129"/>
-      <c r="F195" s="130"/>
+      <c r="A195" s="111"/>
+      <c r="B195" s="106"/>
+      <c r="C195" s="106"/>
+      <c r="D195" s="106"/>
+      <c r="E195" s="106"/>
+      <c r="F195" s="112"/>
     </row>
     <row r="196" spans="1:6" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A196" s="131"/>
-      <c r="B196" s="129"/>
-      <c r="C196" s="129"/>
-      <c r="D196" s="129"/>
-      <c r="E196" s="129"/>
-      <c r="F196" s="130"/>
+      <c r="A196" s="113"/>
+      <c r="B196" s="106"/>
+      <c r="C196" s="106"/>
+      <c r="D196" s="106"/>
+      <c r="E196" s="106"/>
+      <c r="F196" s="112"/>
     </row>
     <row r="197" spans="1:6" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A197" s="132"/>
-      <c r="B197" s="133"/>
-      <c r="C197" s="133"/>
-      <c r="D197" s="133"/>
-      <c r="E197" s="133"/>
-      <c r="F197" s="134"/>
+      <c r="A197" s="114"/>
+      <c r="B197" s="115"/>
+      <c r="C197" s="115"/>
+      <c r="D197" s="115"/>
+      <c r="E197" s="115"/>
+      <c r="F197" s="116"/>
     </row>
   </sheetData>
   <protectedRanges>
     <protectedRange sqref="E66" name="Intervalo1"/>
   </protectedRanges>
   <mergeCells count="39">
+    <mergeCell ref="A145:F147"/>
+    <mergeCell ref="A195:F197"/>
+    <mergeCell ref="G96:M98"/>
+    <mergeCell ref="N96:U98"/>
+    <mergeCell ref="K53:L53"/>
+    <mergeCell ref="B59:E59"/>
+    <mergeCell ref="B108:E108"/>
+    <mergeCell ref="B61:D61"/>
+    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A96:F98"/>
+    <mergeCell ref="G47:M49"/>
+    <mergeCell ref="A8:F8"/>
+    <mergeCell ref="N8:U8"/>
+    <mergeCell ref="G8:M8"/>
+    <mergeCell ref="H44:J44"/>
+    <mergeCell ref="O34:P34"/>
+    <mergeCell ref="B30:E30"/>
+    <mergeCell ref="B12:D12"/>
+    <mergeCell ref="O33:T33"/>
+    <mergeCell ref="N30:U30"/>
+    <mergeCell ref="O38:P38"/>
+    <mergeCell ref="O36:P36"/>
+    <mergeCell ref="N47:U49"/>
     <mergeCell ref="K3:L3"/>
     <mergeCell ref="B157:E157"/>
     <mergeCell ref="O35:P35"/>
@@ -8453,40 +8476,15 @@
     <mergeCell ref="A155:F155"/>
     <mergeCell ref="G57:M57"/>
     <mergeCell ref="A106:F106"/>
-    <mergeCell ref="G47:M49"/>
-    <mergeCell ref="A8:F8"/>
-    <mergeCell ref="N8:U8"/>
-    <mergeCell ref="G8:M8"/>
-    <mergeCell ref="H44:J44"/>
-    <mergeCell ref="O34:P34"/>
-    <mergeCell ref="B30:E30"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="O33:T33"/>
-    <mergeCell ref="N30:U30"/>
-    <mergeCell ref="O38:P38"/>
-    <mergeCell ref="O36:P36"/>
-    <mergeCell ref="N47:U49"/>
-    <mergeCell ref="A145:F147"/>
-    <mergeCell ref="A195:F197"/>
-    <mergeCell ref="G96:M98"/>
-    <mergeCell ref="N96:U98"/>
-    <mergeCell ref="K53:L53"/>
-    <mergeCell ref="B59:E59"/>
-    <mergeCell ref="B108:E108"/>
-    <mergeCell ref="B61:D61"/>
-    <mergeCell ref="A57:F57"/>
-    <mergeCell ref="A96:F98"/>
   </mergeCells>
   <conditionalFormatting sqref="L12:L43">
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
       <formula>0</formula>
     </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="L12:L43">
-    <cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
+    <cfRule type="cellIs" dxfId="1" priority="2" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="2" operator="greaterThan">
+    <cfRule type="cellIs" dxfId="0" priority="3" operator="greaterThan">
       <formula>0</formula>
     </cfRule>
   </conditionalFormatting>
@@ -8569,11 +8567,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -8585,9 +8583,9 @@
         <v>64</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -8600,9 +8598,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -8639,19 +8637,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -8667,17 +8665,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -8743,9 +8741,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -8806,9 +8804,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -8891,9 +8889,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -8931,11 +8929,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'08.26'!B30</f>
+        <f>IFERROR('08.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'08.26'!C30</f>
+        <f>IFERROR('08.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -9057,11 +9055,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -9071,10 +9069,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -9091,10 +9089,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -9105,12 +9103,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'08.26'!C38</f>
+        <f>IFERROR('08.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -9125,10 +9123,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -9142,31 +9140,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'08.26'!C41</f>
+        <f>IFERROR('08.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -9176,17 +9174,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -9198,17 +9196,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -9220,18 +9218,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -9242,10 +9240,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9288,19 +9286,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -9337,7 +9335,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'08.26'!B52</f>
+        <f>IFERROR('08.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -9398,15 +9396,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9420,15 +9418,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9437,15 +9435,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9456,15 +9454,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9472,21 +9470,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'08.26'!B58</f>
+        <f>IFERROR('08.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -9526,10 +9524,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -9570,43 +9568,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -9634,24 +9632,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -9665,11 +9650,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -9750,11 +9748,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -9766,9 +9764,9 @@
         <v>65</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -9781,9 +9779,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -9820,19 +9818,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -9848,17 +9846,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -9924,9 +9922,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -9987,9 +9985,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -10072,9 +10070,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -10112,11 +10110,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'09.26'!B30</f>
+        <f>IFERROR('09.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'09.26'!C30</f>
+        <f>IFERROR('09.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -10238,11 +10236,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -10252,10 +10250,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -10272,10 +10270,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -10286,12 +10284,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'09.26'!C38</f>
+        <f>IFERROR('09.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -10306,10 +10304,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -10323,31 +10321,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'09.26'!C41</f>
+        <f>IFERROR('09.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -10357,17 +10355,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -10379,17 +10377,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -10401,18 +10399,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -10423,10 +10421,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10469,19 +10467,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -10518,7 +10516,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'09.26'!B52</f>
+        <f>IFERROR('09.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -10579,15 +10577,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10601,15 +10599,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10618,15 +10616,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10637,15 +10635,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10653,21 +10651,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'09.26'!B58</f>
+        <f>IFERROR('09.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -10707,10 +10705,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -10751,43 +10749,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -10815,24 +10813,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -10846,11 +10831,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -10931,11 +10929,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -10947,9 +10945,9 @@
         <v>66</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -10962,9 +10960,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -11001,19 +10999,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -11029,17 +11027,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -11105,9 +11103,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -11168,9 +11166,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -11253,9 +11251,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -11293,11 +11291,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'10.26'!B30</f>
+        <f>IFERROR('10.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'10.26'!C30</f>
+        <f>IFERROR('10.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -11419,11 +11417,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -11433,10 +11431,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -11453,10 +11451,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -11467,12 +11465,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'10.26'!C38</f>
+        <f>IFERROR('10.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -11487,10 +11485,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -11504,31 +11502,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'10.26'!C41</f>
+        <f>IFERROR('10.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -11538,17 +11536,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -11560,17 +11558,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -11582,18 +11580,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -11604,10 +11602,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11650,19 +11648,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -11699,7 +11697,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'10.26'!B52</f>
+        <f>IFERROR('10.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -11760,15 +11758,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11782,15 +11780,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11799,15 +11797,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11818,15 +11816,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11834,21 +11832,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'10.26'!B58</f>
+        <f>IFERROR('10.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -11888,10 +11886,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -11932,43 +11930,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -11996,24 +11994,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -12027,11 +12012,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -12112,11 +12110,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -12128,9 +12126,9 @@
         <v>67</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -12143,9 +12141,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -12182,19 +12180,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -12210,17 +12208,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -12286,9 +12284,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -12349,9 +12347,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -12434,9 +12432,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -12474,11 +12472,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'11.26'!B30</f>
+        <f>IFERROR('11.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'11.26'!C30</f>
+        <f>IFERROR('11.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -12600,11 +12598,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -12614,10 +12612,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -12634,10 +12632,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -12648,12 +12646,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'11.26'!C38</f>
+        <f>IFERROR('11.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -12668,10 +12666,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -12685,31 +12683,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'11.26'!C41</f>
+        <f>IFERROR('11.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -12719,17 +12717,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -12741,17 +12739,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -12763,18 +12761,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -12785,10 +12783,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12831,19 +12829,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -12880,7 +12878,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'11.26'!B52</f>
+        <f>IFERROR('11.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -12941,15 +12939,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12963,15 +12961,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12980,15 +12978,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -12999,15 +12997,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13015,21 +13013,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'11.26'!B58</f>
+        <f>IFERROR('11.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -13069,10 +13067,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -13113,43 +13111,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -13177,24 +13175,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -13208,11 +13193,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -13293,11 +13291,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -13309,9 +13307,9 @@
         <v>57</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -13324,9 +13322,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -13363,19 +13361,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -13391,17 +13389,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -13467,9 +13465,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -13530,9 +13528,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -13615,9 +13613,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -13655,11 +13653,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'2026'!E32</f>
+        <f>IFERROR('2026'!E32,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'2026'!E12</f>
+        <f>IFERROR('2026'!E12,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -13781,11 +13779,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -13795,10 +13793,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -13815,10 +13813,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -13829,10 +13827,10 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="31"/>
       <c r="D37" s="13"/>
       <c r="E37" s="14"/>
@@ -13846,10 +13844,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -13863,29 +13861,29 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="31"/>
       <c r="D40" s="13"/>
       <c r="E40" s="14"/>
@@ -13894,17 +13892,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -13916,17 +13914,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -13938,18 +13936,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -13960,10 +13958,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14006,19 +14004,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -14055,7 +14053,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="31">
-        <f>'2026'!E61</f>
+        <f>IFERROR('2026'!E61,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -14116,15 +14114,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14138,15 +14136,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14155,15 +14153,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14174,15 +14172,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14193,15 +14191,15 @@
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -14241,10 +14239,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -14285,43 +14283,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -14349,24 +14347,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -14380,11 +14365,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -14465,11 +14463,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -14481,9 +14479,9 @@
         <v>58</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -14496,9 +14494,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -14535,19 +14533,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -14563,17 +14561,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -14639,9 +14637,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -14702,9 +14700,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -14787,9 +14785,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -14827,11 +14825,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'01.26'!B30</f>
+        <f>IFERROR('01.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'01.26'!C30</f>
+        <f>IFERROR('01.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -14953,11 +14951,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -14967,10 +14965,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -14987,10 +14985,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -15001,12 +14999,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'01.26'!C38</f>
+        <f>IFERROR('01.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -15021,10 +15019,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -15038,31 +15036,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'01.26'!C41</f>
+        <f>IFERROR('01.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -15072,17 +15070,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -15094,17 +15092,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -15116,18 +15114,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -15138,10 +15136,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15184,19 +15182,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -15233,7 +15231,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'01.26'!B52</f>
+        <f>IFERROR('01.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -15294,15 +15292,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15316,15 +15314,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15333,15 +15331,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15352,15 +15350,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15368,21 +15366,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'01.26'!B58</f>
+        <f>IFERROR('01.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -15422,10 +15420,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -15466,43 +15464,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -15530,24 +15528,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -15561,11 +15546,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -15646,11 +15644,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -15662,9 +15660,9 @@
         <v>59</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -15677,9 +15675,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -15716,19 +15714,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -15744,17 +15742,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -15820,9 +15818,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -15883,9 +15881,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -15968,9 +15966,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -16008,11 +16006,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'02.26'!B30</f>
+        <f>IFERROR('02.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'02.26'!C30</f>
+        <f>IFERROR('02.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -16134,11 +16132,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -16148,10 +16146,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -16168,10 +16166,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -16182,12 +16180,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'02.26'!C38</f>
+        <f>IFERROR('02.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -16202,10 +16200,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -16219,31 +16217,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'02.26'!C41</f>
+        <f>IFERROR('02.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -16253,17 +16251,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -16275,17 +16273,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -16297,18 +16295,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -16319,10 +16317,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16365,19 +16363,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -16414,7 +16412,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'02.26'!B52</f>
+        <f>IFERROR('02.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -16475,15 +16473,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16497,15 +16495,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16514,15 +16512,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16533,15 +16531,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16549,21 +16547,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'02.26'!B58</f>
+        <f>IFERROR('02.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -16603,10 +16601,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -16647,43 +16645,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -16711,24 +16709,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -16742,11 +16727,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -16827,11 +16825,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -16843,9 +16841,9 @@
         <v>60</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -16858,9 +16856,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -16897,19 +16895,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -16925,17 +16923,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -17001,9 +16999,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -17064,9 +17062,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -17149,9 +17147,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -17189,11 +17187,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'03.26'!B30</f>
+        <f>IFERROR('03.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'03.26'!C30</f>
+        <f>IFERROR('03.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -17315,11 +17313,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -17329,10 +17327,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -17349,10 +17347,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -17363,12 +17361,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'03.26'!C38</f>
+        <f>IFERROR('03.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -17383,10 +17381,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -17400,31 +17398,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'03.26'!C41</f>
+        <f>IFERROR('03.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -17434,17 +17432,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -17456,17 +17454,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -17478,18 +17476,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -17500,10 +17498,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17546,19 +17544,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -17595,7 +17593,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'03.26'!B52</f>
+        <f>IFERROR('03.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -17656,15 +17654,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17678,15 +17676,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17695,15 +17693,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17714,15 +17712,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17730,21 +17728,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'03.26'!B58</f>
+        <f>IFERROR('03.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -17784,10 +17782,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -17828,43 +17826,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -17892,24 +17890,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -17923,11 +17908,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -18008,11 +18006,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -18024,9 +18022,9 @@
         <v>0</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -18039,9 +18037,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -18078,19 +18076,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -18106,17 +18104,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -18182,9 +18180,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -18245,9 +18243,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -18330,9 +18328,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -18370,11 +18368,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'04.26'!B30</f>
+        <f>IFERROR('04.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'04.26'!C30</f>
+        <f>IFERROR('04.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -18496,11 +18494,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -18510,10 +18508,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -18530,10 +18528,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -18544,12 +18542,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'04.26'!C38</f>
+        <f>IFERROR('04.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -18564,10 +18562,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -18581,31 +18579,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'04.26'!C41</f>
+        <f>IFERROR('04.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -18615,17 +18613,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -18637,17 +18635,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -18659,18 +18657,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -18681,10 +18679,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18727,19 +18725,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -18776,7 +18774,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'04.26'!B52</f>
+        <f>IFERROR('04.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -18837,15 +18835,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18859,15 +18857,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18876,15 +18874,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18895,15 +18893,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18911,21 +18909,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'04.26'!B58</f>
+        <f>IFERROR('04.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -18965,10 +18963,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -19009,43 +19007,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -19073,24 +19071,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -19104,11 +19089,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -19189,11 +19187,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -19205,9 +19203,9 @@
         <v>61</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -19220,9 +19218,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -19259,19 +19257,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -19287,17 +19285,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -19363,9 +19361,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -19426,9 +19424,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -19511,9 +19509,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -19551,11 +19549,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'05.26'!B30</f>
+        <f>IFERROR('05.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'05.26'!C30</f>
+        <f>IFERROR('05.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -19677,11 +19675,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -19691,10 +19689,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -19711,10 +19709,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -19725,12 +19723,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'05.26'!C38</f>
+        <f>IFERROR('05.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -19745,10 +19743,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -19762,31 +19760,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'05.26'!C41</f>
+        <f>IFERROR('05.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -19796,17 +19794,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -19818,17 +19816,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -19840,18 +19838,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -19862,10 +19860,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -19908,19 +19906,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -19957,7 +19955,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'05.26'!B52</f>
+        <f>IFERROR('05.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -20018,15 +20016,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20040,15 +20038,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20057,15 +20055,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20076,15 +20074,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20092,21 +20090,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'05.26'!B58</f>
+        <f>IFERROR('05.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -20146,10 +20144,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -20190,43 +20188,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -20254,24 +20252,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -20285,11 +20270,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -20370,11 +20368,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -20386,9 +20384,9 @@
         <v>62</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -20401,9 +20399,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -20440,19 +20438,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -20468,17 +20466,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -20544,9 +20542,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -20607,9 +20605,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -20692,9 +20690,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -20732,11 +20730,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'06.26'!B30</f>
+        <f>IFERROR('06.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'06.26'!C30</f>
+        <f>IFERROR('06.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -20858,11 +20856,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -20872,10 +20870,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -20892,10 +20890,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -20906,12 +20904,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'06.26'!C38</f>
+        <f>IFERROR('06.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -20926,10 +20924,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -20943,31 +20941,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'06.26'!C41</f>
+        <f>IFERROR('06.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -20977,17 +20975,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -20999,17 +20997,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -21021,18 +21019,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -21043,10 +21041,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21089,19 +21087,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -21138,7 +21136,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'06.26'!B52</f>
+        <f>IFERROR('06.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -21199,15 +21197,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21221,15 +21219,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21238,15 +21236,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21257,15 +21255,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21273,21 +21271,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'06.26'!B58</f>
+        <f>IFERROR('06.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -21327,10 +21325,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -21371,43 +21369,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -21435,24 +21433,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -21466,11 +21451,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
@@ -21551,11 +21549,11 @@
     </row>
     <row r="5" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="5"/>
-      <c r="B5" s="118"/>
-      <c r="C5" s="104"/>
-      <c r="D5" s="104"/>
-      <c r="E5" s="104"/>
-      <c r="F5" s="104"/>
+      <c r="B5" s="135"/>
+      <c r="C5" s="136"/>
+      <c r="D5" s="136"/>
+      <c r="E5" s="136"/>
+      <c r="F5" s="136"/>
       <c r="G5" s="9"/>
       <c r="H5" s="9"/>
       <c r="I5" s="9"/>
@@ -21567,9 +21565,9 @@
         <v>63</v>
       </c>
       <c r="B6" s="4"/>
-      <c r="C6" s="119"/>
-      <c r="D6" s="104"/>
-      <c r="E6" s="104"/>
+      <c r="C6" s="137"/>
+      <c r="D6" s="136"/>
+      <c r="E6" s="136"/>
       <c r="F6" s="4"/>
       <c r="G6" s="4"/>
       <c r="H6" s="4"/>
@@ -21582,9 +21580,9 @@
         <v>53</v>
       </c>
       <c r="B7" s="4"/>
-      <c r="C7" s="119"/>
-      <c r="D7" s="104"/>
-      <c r="E7" s="104"/>
+      <c r="C7" s="137"/>
+      <c r="D7" s="136"/>
+      <c r="E7" s="136"/>
       <c r="F7" s="4"/>
       <c r="G7" s="4"/>
       <c r="H7" s="4"/>
@@ -21621,19 +21619,19 @@
       <c r="K9" s="6"/>
     </row>
     <row r="10" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="120" t="s">
+      <c r="A10" s="138" t="s">
         <v>1</v>
       </c>
-      <c r="B10" s="121"/>
-      <c r="C10" s="121"/>
-      <c r="D10" s="121"/>
-      <c r="E10" s="121"/>
-      <c r="F10" s="121"/>
-      <c r="G10" s="121"/>
-      <c r="H10" s="121"/>
-      <c r="I10" s="121"/>
-      <c r="J10" s="121"/>
-      <c r="K10" s="122"/>
+      <c r="B10" s="139"/>
+      <c r="C10" s="139"/>
+      <c r="D10" s="139"/>
+      <c r="E10" s="139"/>
+      <c r="F10" s="139"/>
+      <c r="G10" s="139"/>
+      <c r="H10" s="139"/>
+      <c r="I10" s="139"/>
+      <c r="J10" s="139"/>
+      <c r="K10" s="140"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A11" s="5"/>
@@ -21649,17 +21647,17 @@
       <c r="K11" s="6"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A12" s="123"/>
-      <c r="B12" s="104"/>
-      <c r="C12" s="104"/>
-      <c r="D12" s="104"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="104"/>
-      <c r="G12" s="104"/>
-      <c r="H12" s="104"/>
-      <c r="I12" s="104"/>
-      <c r="J12" s="104"/>
-      <c r="K12" s="117"/>
+      <c r="A12" s="141"/>
+      <c r="B12" s="136"/>
+      <c r="C12" s="136"/>
+      <c r="D12" s="136"/>
+      <c r="E12" s="136"/>
+      <c r="F12" s="136"/>
+      <c r="G12" s="136"/>
+      <c r="H12" s="136"/>
+      <c r="I12" s="136"/>
+      <c r="J12" s="136"/>
+      <c r="K12" s="142"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
@@ -21725,9 +21723,9 @@
       <c r="K16" s="15"/>
     </row>
     <row r="17" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="124"/>
-      <c r="B17" s="125"/>
-      <c r="C17" s="114"/>
+      <c r="A17" s="143"/>
+      <c r="B17" s="144"/>
+      <c r="C17" s="134"/>
       <c r="D17" s="13"/>
       <c r="E17" s="14"/>
       <c r="G17" s="14"/>
@@ -21788,9 +21786,9 @@
       <c r="K20" s="15"/>
     </row>
     <row r="21" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="124"/>
-      <c r="B21" s="125"/>
-      <c r="C21" s="114"/>
+      <c r="A21" s="143"/>
+      <c r="B21" s="144"/>
+      <c r="C21" s="134"/>
       <c r="D21" s="13"/>
       <c r="E21" s="14"/>
       <c r="F21" s="14" t="s">
@@ -21873,9 +21871,9 @@
       <c r="K25" s="15"/>
     </row>
     <row r="26" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="126"/>
-      <c r="B26" s="125"/>
-      <c r="C26" s="114"/>
+      <c r="A26" s="145"/>
+      <c r="B26" s="144"/>
+      <c r="C26" s="134"/>
       <c r="D26" s="13"/>
       <c r="E26" s="14"/>
       <c r="F26" s="7" t="s">
@@ -21913,11 +21911,11 @@
         <v>21</v>
       </c>
       <c r="B28" s="24">
-        <f>'07.26'!B30</f>
+        <f>IFERROR('07.26'!B30,0)</f>
         <v>0</v>
       </c>
       <c r="C28" s="24">
-        <f>'07.26'!C30</f>
+        <f>IFERROR('07.26'!C30,0)</f>
         <v>0</v>
       </c>
       <c r="D28" s="13"/>
@@ -22039,11 +22037,11 @@
       <c r="K33" s="15"/>
     </row>
     <row r="34" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="127" t="s">
+      <c r="A34" s="146" t="s">
         <v>26</v>
       </c>
-      <c r="B34" s="125"/>
-      <c r="C34" s="114"/>
+      <c r="B34" s="144"/>
+      <c r="C34" s="134"/>
       <c r="D34" s="13"/>
       <c r="E34" s="14"/>
       <c r="G34" s="14"/>
@@ -22053,10 +22051,10 @@
       <c r="K34" s="15"/>
     </row>
     <row r="35" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="113" t="s">
+      <c r="A35" s="133" t="s">
         <v>28</v>
       </c>
-      <c r="B35" s="114"/>
+      <c r="B35" s="134"/>
       <c r="C35" s="31">
         <f>B32+C32</f>
         <v>0</v>
@@ -22073,10 +22071,10 @@
       <c r="K35" s="15"/>
     </row>
     <row r="36" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="113" t="s">
+      <c r="A36" s="133" t="s">
         <v>29</v>
       </c>
-      <c r="B36" s="114"/>
+      <c r="B36" s="134"/>
       <c r="C36" s="31"/>
       <c r="D36" s="13"/>
       <c r="E36" s="14"/>
@@ -22087,12 +22085,12 @@
       <c r="K36" s="15"/>
     </row>
     <row r="37" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="113" t="s">
+      <c r="A37" s="133" t="s">
         <v>31</v>
       </c>
-      <c r="B37" s="114"/>
+      <c r="B37" s="134"/>
       <c r="C37" s="24">
-        <f>'07.26'!C38</f>
+        <f>IFERROR('07.26'!C38,0)</f>
         <v>0</v>
       </c>
       <c r="D37" s="13"/>
@@ -22107,10 +22105,10 @@
       <c r="K37" s="15"/>
     </row>
     <row r="38" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="113" t="s">
+      <c r="A38" s="133" t="s">
         <v>32</v>
       </c>
-      <c r="B38" s="114"/>
+      <c r="B38" s="134"/>
       <c r="C38" s="31">
         <f>MAX(0,C36+C37-C32)</f>
         <v>0</v>
@@ -22124,31 +22122,31 @@
       <c r="K38" s="15"/>
     </row>
     <row r="39" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="113" t="s">
+      <c r="A39" s="133" t="s">
         <v>34</v>
       </c>
-      <c r="B39" s="114"/>
+      <c r="B39" s="134"/>
       <c r="C39" s="31"/>
       <c r="D39" s="13"/>
       <c r="E39" s="14"/>
-      <c r="F39" s="103" t="s">
+      <c r="F39" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G39" s="103"/>
-      <c r="H39" s="103"/>
-      <c r="I39" s="105">
-        <v>0</v>
-      </c>
-      <c r="J39" s="105"/>
+      <c r="G39" s="147"/>
+      <c r="H39" s="147"/>
+      <c r="I39" s="148">
+        <v>0</v>
+      </c>
+      <c r="J39" s="148"/>
       <c r="K39" s="15"/>
     </row>
     <row r="40" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="113" t="s">
+      <c r="A40" s="133" t="s">
         <v>36</v>
       </c>
-      <c r="B40" s="114"/>
+      <c r="B40" s="134"/>
       <c r="C40" s="24">
-        <f>'07.26'!C41</f>
+        <f>IFERROR('07.26'!C41,0)</f>
         <v>0</v>
       </c>
       <c r="D40" s="13"/>
@@ -22158,17 +22156,17 @@
       </c>
       <c r="G40" s="40"/>
       <c r="H40" s="40"/>
-      <c r="I40" s="105">
-        <v>0</v>
-      </c>
-      <c r="J40" s="105"/>
+      <c r="I40" s="148">
+        <v>0</v>
+      </c>
+      <c r="J40" s="148"/>
       <c r="K40" s="15"/>
     </row>
     <row r="41" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="113" t="s">
+      <c r="A41" s="133" t="s">
         <v>38</v>
       </c>
-      <c r="B41" s="114"/>
+      <c r="B41" s="134"/>
       <c r="C41" s="31">
         <f>MAX(0,C39+C40-B32)</f>
         <v>0</v>
@@ -22180,17 +22178,17 @@
       </c>
       <c r="G41" s="40"/>
       <c r="H41" s="40"/>
-      <c r="I41" s="105">
-        <v>0</v>
-      </c>
-      <c r="J41" s="105"/>
+      <c r="I41" s="148">
+        <v>0</v>
+      </c>
+      <c r="J41" s="148"/>
       <c r="K41" s="15"/>
     </row>
     <row r="42" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="115" t="s">
+      <c r="A42" s="149" t="s">
         <v>40</v>
       </c>
-      <c r="B42" s="114"/>
+      <c r="B42" s="134"/>
       <c r="C42" s="33">
         <f>MAX(0,C32-(C36+C37))+MAX(0,B32-(C39+C40))</f>
         <v>0</v>
@@ -22202,18 +22200,18 @@
       </c>
       <c r="G42" s="40"/>
       <c r="H42" s="40"/>
-      <c r="I42" s="105">
-        <v>0</v>
-      </c>
-      <c r="J42" s="105"/>
+      <c r="I42" s="148">
+        <v>0</v>
+      </c>
+      <c r="J42" s="148"/>
       <c r="K42" s="15"/>
     </row>
     <row r="43" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="113" t="s">
+      <c r="A43" s="133" t="s">
         <v>42</v>
       </c>
-      <c r="B43" s="114"/>
-      <c r="C43" s="156" t="str">
+      <c r="B43" s="134"/>
+      <c r="C43" s="103" t="str">
         <f>IF($C$42&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -22224,10 +22222,10 @@
       </c>
       <c r="G43" s="40"/>
       <c r="H43" s="40"/>
-      <c r="I43" s="105">
-        <v>0</v>
-      </c>
-      <c r="J43" s="105"/>
+      <c r="I43" s="148">
+        <v>0</v>
+      </c>
+      <c r="J43" s="148"/>
       <c r="K43" s="15"/>
     </row>
     <row r="44" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22270,19 +22268,19 @@
       <c r="K46" s="15"/>
     </row>
     <row r="47" spans="1:11" ht="17.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="116" t="s">
+      <c r="A47" s="150" t="s">
         <v>43</v>
       </c>
-      <c r="B47" s="104"/>
-      <c r="C47" s="104"/>
-      <c r="D47" s="104"/>
-      <c r="E47" s="104"/>
-      <c r="F47" s="104"/>
-      <c r="G47" s="104"/>
-      <c r="H47" s="104"/>
-      <c r="I47" s="104"/>
-      <c r="J47" s="104"/>
-      <c r="K47" s="117"/>
+      <c r="B47" s="136"/>
+      <c r="C47" s="136"/>
+      <c r="D47" s="136"/>
+      <c r="E47" s="136"/>
+      <c r="F47" s="136"/>
+      <c r="G47" s="136"/>
+      <c r="H47" s="136"/>
+      <c r="I47" s="136"/>
+      <c r="J47" s="136"/>
+      <c r="K47" s="142"/>
     </row>
     <row r="48" spans="1:11" ht="21" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A48" s="30"/>
@@ -22319,7 +22317,7 @@
         <v>46</v>
       </c>
       <c r="B50" s="24">
-        <f>'07.26'!B52</f>
+        <f>IFERROR('07.26'!B52,0)</f>
         <v>0</v>
       </c>
       <c r="C50" s="14"/>
@@ -22380,15 +22378,15 @@
       <c r="C53" s="14"/>
       <c r="D53" s="13"/>
       <c r="E53" s="14"/>
-      <c r="F53" s="103" t="s">
+      <c r="F53" s="147" t="s">
         <v>33</v>
       </c>
-      <c r="G53" s="104"/>
-      <c r="H53" s="104"/>
-      <c r="I53" s="105">
-        <v>0</v>
-      </c>
-      <c r="J53" s="104"/>
+      <c r="G53" s="136"/>
+      <c r="H53" s="136"/>
+      <c r="I53" s="148">
+        <v>0</v>
+      </c>
+      <c r="J53" s="136"/>
       <c r="K53" s="15"/>
     </row>
     <row r="54" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22402,15 +22400,15 @@
       <c r="C54" s="14"/>
       <c r="D54" s="13"/>
       <c r="E54" s="14"/>
-      <c r="F54" s="103" t="s">
+      <c r="F54" s="147" t="s">
         <v>35</v>
       </c>
-      <c r="G54" s="104"/>
-      <c r="H54" s="104"/>
-      <c r="I54" s="105">
-        <v>0</v>
-      </c>
-      <c r="J54" s="104"/>
+      <c r="G54" s="136"/>
+      <c r="H54" s="136"/>
+      <c r="I54" s="148">
+        <v>0</v>
+      </c>
+      <c r="J54" s="136"/>
       <c r="K54" s="15"/>
     </row>
     <row r="55" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22419,15 +22417,15 @@
       <c r="C55" s="14"/>
       <c r="D55" s="13"/>
       <c r="E55" s="14"/>
-      <c r="F55" s="103" t="s">
+      <c r="F55" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="G55" s="104"/>
-      <c r="H55" s="104"/>
-      <c r="I55" s="105">
-        <v>0</v>
-      </c>
-      <c r="J55" s="104"/>
+      <c r="G55" s="136"/>
+      <c r="H55" s="136"/>
+      <c r="I55" s="148">
+        <v>0</v>
+      </c>
+      <c r="J55" s="136"/>
       <c r="K55" s="15"/>
     </row>
     <row r="56" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22438,15 +22436,15 @@
       <c r="C56" s="14"/>
       <c r="D56" s="13"/>
       <c r="E56" s="14"/>
-      <c r="F56" s="103" t="s">
+      <c r="F56" s="147" t="s">
         <v>39</v>
       </c>
-      <c r="G56" s="104"/>
-      <c r="H56" s="104"/>
-      <c r="I56" s="105">
-        <v>0</v>
-      </c>
-      <c r="J56" s="104"/>
+      <c r="G56" s="136"/>
+      <c r="H56" s="136"/>
+      <c r="I56" s="148">
+        <v>0</v>
+      </c>
+      <c r="J56" s="136"/>
       <c r="K56" s="15"/>
     </row>
     <row r="57" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22454,21 +22452,21 @@
         <v>51</v>
       </c>
       <c r="B57" s="24">
-        <f>'07.26'!B58</f>
+        <f>IFERROR('07.26'!B58,0)</f>
         <v>0</v>
       </c>
       <c r="C57" s="14"/>
       <c r="D57" s="13"/>
       <c r="E57" s="14"/>
-      <c r="F57" s="103" t="s">
+      <c r="F57" s="147" t="s">
         <v>41</v>
       </c>
-      <c r="G57" s="104"/>
-      <c r="H57" s="104"/>
-      <c r="I57" s="105">
-        <v>0</v>
-      </c>
-      <c r="J57" s="104"/>
+      <c r="G57" s="136"/>
+      <c r="H57" s="136"/>
+      <c r="I57" s="148">
+        <v>0</v>
+      </c>
+      <c r="J57" s="136"/>
       <c r="K57" s="15"/>
     </row>
     <row r="58" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
@@ -22508,10 +22506,10 @@
       <c r="K59" s="15"/>
     </row>
     <row r="60" spans="1:11" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A60" s="157" t="s">
+      <c r="A60" s="104" t="s">
         <v>42</v>
       </c>
-      <c r="B60" s="156" t="str">
+      <c r="B60" s="103" t="str">
         <f>IF($B$59&gt;=10,WORKDAY(EOMONTH(DATE(2000+VALUE(RIGHT($A$6,2)),VALUE(MID($A$6,FIND(": ",$A$6)+2,2)),1),1)+1,-1),"")</f>
         <v/>
       </c>
@@ -22552,43 +22550,43 @@
       <c r="K62" s="6"/>
     </row>
     <row r="63" spans="1:11" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A63" s="106"/>
-      <c r="B63" s="107"/>
-      <c r="C63" s="107"/>
-      <c r="D63" s="107"/>
-      <c r="E63" s="107"/>
-      <c r="F63" s="107"/>
-      <c r="G63" s="107"/>
-      <c r="H63" s="107"/>
-      <c r="I63" s="107"/>
-      <c r="J63" s="107"/>
-      <c r="K63" s="108"/>
+      <c r="A63" s="151"/>
+      <c r="B63" s="152"/>
+      <c r="C63" s="152"/>
+      <c r="D63" s="152"/>
+      <c r="E63" s="152"/>
+      <c r="F63" s="152"/>
+      <c r="G63" s="152"/>
+      <c r="H63" s="152"/>
+      <c r="I63" s="152"/>
+      <c r="J63" s="152"/>
+      <c r="K63" s="153"/>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.25">
-      <c r="A64" s="109"/>
-      <c r="B64" s="107"/>
-      <c r="C64" s="107"/>
-      <c r="D64" s="107"/>
-      <c r="E64" s="107"/>
-      <c r="F64" s="107"/>
-      <c r="G64" s="107"/>
-      <c r="H64" s="107"/>
-      <c r="I64" s="107"/>
-      <c r="J64" s="107"/>
-      <c r="K64" s="108"/>
+      <c r="A64" s="154"/>
+      <c r="B64" s="152"/>
+      <c r="C64" s="152"/>
+      <c r="D64" s="152"/>
+      <c r="E64" s="152"/>
+      <c r="F64" s="152"/>
+      <c r="G64" s="152"/>
+      <c r="H64" s="152"/>
+      <c r="I64" s="152"/>
+      <c r="J64" s="152"/>
+      <c r="K64" s="153"/>
     </row>
     <row r="65" spans="1:11" ht="17.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A65" s="110"/>
-      <c r="B65" s="111"/>
-      <c r="C65" s="111"/>
-      <c r="D65" s="111"/>
-      <c r="E65" s="111"/>
-      <c r="F65" s="111"/>
-      <c r="G65" s="111"/>
-      <c r="H65" s="111"/>
-      <c r="I65" s="111"/>
-      <c r="J65" s="111"/>
-      <c r="K65" s="112"/>
+      <c r="A65" s="155"/>
+      <c r="B65" s="156"/>
+      <c r="C65" s="156"/>
+      <c r="D65" s="156"/>
+      <c r="E65" s="156"/>
+      <c r="F65" s="156"/>
+      <c r="G65" s="156"/>
+      <c r="H65" s="156"/>
+      <c r="I65" s="156"/>
+      <c r="J65" s="156"/>
+      <c r="K65" s="157"/>
     </row>
     <row r="68" spans="1:11" ht="15" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="72" spans="1:11" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -22616,24 +22614,11 @@
     <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="36">
-    <mergeCell ref="A37:B37"/>
-    <mergeCell ref="B5:F5"/>
-    <mergeCell ref="C6:E6"/>
-    <mergeCell ref="C7:E7"/>
-    <mergeCell ref="A10:K10"/>
-    <mergeCell ref="A12:K12"/>
-    <mergeCell ref="A17:C17"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="A34:C34"/>
-    <mergeCell ref="A35:B35"/>
-    <mergeCell ref="A36:B36"/>
-    <mergeCell ref="A38:B38"/>
-    <mergeCell ref="A39:B39"/>
-    <mergeCell ref="F39:H39"/>
-    <mergeCell ref="I39:J39"/>
-    <mergeCell ref="A40:B40"/>
-    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="F56:H56"/>
+    <mergeCell ref="I56:J56"/>
+    <mergeCell ref="F57:H57"/>
+    <mergeCell ref="I57:J57"/>
+    <mergeCell ref="A63:K65"/>
     <mergeCell ref="F55:H55"/>
     <mergeCell ref="I55:J55"/>
     <mergeCell ref="A41:B41"/>
@@ -22647,11 +22632,24 @@
     <mergeCell ref="I53:J53"/>
     <mergeCell ref="F54:H54"/>
     <mergeCell ref="I54:J54"/>
-    <mergeCell ref="F56:H56"/>
-    <mergeCell ref="I56:J56"/>
-    <mergeCell ref="F57:H57"/>
-    <mergeCell ref="I57:J57"/>
-    <mergeCell ref="A63:K65"/>
+    <mergeCell ref="A38:B38"/>
+    <mergeCell ref="A39:B39"/>
+    <mergeCell ref="F39:H39"/>
+    <mergeCell ref="I39:J39"/>
+    <mergeCell ref="A40:B40"/>
+    <mergeCell ref="I40:J40"/>
+    <mergeCell ref="A37:B37"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="C6:E6"/>
+    <mergeCell ref="C7:E7"/>
+    <mergeCell ref="A10:K10"/>
+    <mergeCell ref="A12:K12"/>
+    <mergeCell ref="A17:C17"/>
+    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A34:C34"/>
+    <mergeCell ref="A35:B35"/>
+    <mergeCell ref="A36:B36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0" right="0" top="0.19685039370078741" bottom="0" header="0" footer="0"/>
